--- a/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NUEVO_CHIMBOTE</t>
+          <t>NUEVO CHIMBOTE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>VIRGEN DE LAS GRACIAS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.11421</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-78.51354000000001</v>
-      </c>
-      <c r="I2" t="n">
-        <v>737</v>
-      </c>
-      <c r="J2" t="n">
-        <v>51</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.11421</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-78.51354</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.125030000000001</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-78.5192</v>
-      </c>
-      <c r="I3" t="n">
-        <v>225</v>
-      </c>
-      <c r="J3" t="n">
-        <v>10</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.12503</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-78.5192</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>1570</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.124029999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-78.52777</v>
-      </c>
-      <c r="I4" t="n">
-        <v>224</v>
-      </c>
-      <c r="J4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.12403</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-78.52777</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>88021 ALFONSO UGARTE</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.134819999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-78.51913999999999</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1062</v>
-      </c>
-      <c r="J5" t="n">
-        <v>66</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.13482</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-78.51914</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>88024</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.12237</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-78.54073</v>
-      </c>
-      <c r="I6" t="n">
-        <v>332</v>
-      </c>
-      <c r="J6" t="n">
-        <v>20</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.12237</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-78.54073</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>88028 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.119109999999999</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-78.54416999999999</v>
-      </c>
-      <c r="I7" t="n">
-        <v>559</v>
-      </c>
-      <c r="J7" t="n">
-        <v>27</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.11911</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-78.54417</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>88047 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.127230000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-78.52884</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2136</v>
-      </c>
-      <c r="J8" t="n">
-        <v>96</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.12723</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-78.52884</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>88061 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.115550000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-78.51434999999999</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J9" t="n">
-        <v>48</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.11555</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-78.51435</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>88227 PEDRO PABLO ATUSPARIA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.12505</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-78.51515000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1455</v>
-      </c>
-      <c r="J10" t="n">
-        <v>62</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.12505</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-78.51515</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>88240 PAZ Y AMISTAD</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.13137</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-78.51621</v>
-      </c>
-      <c r="I11" t="n">
-        <v>625</v>
-      </c>
-      <c r="J11" t="n">
-        <v>29</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.13137</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-78.51621</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>88298 LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.10938</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-78.53254</v>
-      </c>
-      <c r="I12" t="n">
-        <v>845</v>
-      </c>
-      <c r="J12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.10938</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-78.53254</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>88336 GASTON VIDAL PORTURAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.120649999999999</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-78.51690000000001</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1886</v>
-      </c>
-      <c r="J13" t="n">
-        <v>82</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.12065</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-78.5169</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>88388 SAN LUIS DE LA PAZ</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.137669000000001</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-78.510127</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1219</v>
-      </c>
-      <c r="J14" t="n">
-        <v>60</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.137669</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-78.510127</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>REPUBLICA ARGENTINA</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-9.12585</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-78.52682</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1615</v>
-      </c>
-      <c r="J15" t="n">
-        <v>79</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-9.12585</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-78.52682</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>VILLA MARIA</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-9.120710000000001</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-78.54867</v>
-      </c>
-      <c r="I16" t="n">
-        <v>873</v>
-      </c>
-      <c r="J16" t="n">
-        <v>54</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-9.12071</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-78.54867</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>88389 JUAN VALER SANDOVAL</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-9.11655</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-78.50554</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1454</v>
-      </c>
-      <c r="J17" t="n">
-        <v>65</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-9.11655</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-78.50554</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>R. F. S. DE YUGOSLAVIA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-9.132250000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-78.5205</v>
-      </c>
-      <c r="I18" t="n">
-        <v>756</v>
-      </c>
-      <c r="J18" t="n">
-        <v>43</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-9.13225</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-78.5205</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>88042</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-9.14711</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-78.50740999999999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>982</v>
-      </c>
-      <c r="J19" t="n">
-        <v>52</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-9.14711</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-78.50741</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>FE Y ALEGRIA 14</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-9.113530000000001</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-78.536861</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1521</v>
-      </c>
-      <c r="J20" t="n">
-        <v>76</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-9.11353</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-78.536861</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1521</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CRISTO AMIGO</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-9.129989999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-78.52722</v>
-      </c>
-      <c r="I21" t="n">
-        <v>454</v>
-      </c>
-      <c r="J21" t="n">
-        <v>42</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-9.12999</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-78.52722</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>MARIA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-9.125590000000001</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-78.52934999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>280</v>
-      </c>
-      <c r="J22" t="n">
-        <v>31</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-9.12559</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-78.52935</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>NORTON SCHOOL</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-9.1364</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-78.52079999999999</v>
-      </c>
-      <c r="I23" t="n">
-        <v>229</v>
-      </c>
-      <c r="J23" t="n">
-        <v>15</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-9.1364</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-78.5208</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>SEMILLITAS &amp; DOLORIER</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-9.12087</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-78.51751</v>
-      </c>
-      <c r="I24" t="n">
-        <v>173</v>
-      </c>
-      <c r="J24" t="n">
-        <v>9</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-9.12087</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-78.51751</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>SANTA MARIA DE CERVELLO</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-9.12313</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-78.53166</v>
-      </c>
-      <c r="I25" t="n">
-        <v>784</v>
-      </c>
-      <c r="J25" t="n">
-        <v>42</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-9.12313</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-78.53166</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>784</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>EXPERIMENTAL UNIVERSIDAD NACIONAL DEL SANTA</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-9.12321</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-78.51109</v>
-      </c>
-      <c r="I26" t="n">
-        <v>698</v>
-      </c>
-      <c r="J26" t="n">
-        <v>38</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-9.12321</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-78.51109</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>88404</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-9.147489999999999</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-78.50353</v>
-      </c>
-      <c r="I27" t="n">
-        <v>463</v>
-      </c>
-      <c r="J27" t="n">
-        <v>20</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-9.14749</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-78.50353</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>JESUS MAESTRO</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-9.119350000000001</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-78.52296</v>
-      </c>
-      <c r="I28" t="n">
-        <v>725</v>
-      </c>
-      <c r="J28" t="n">
-        <v>37</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-9.11935</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-78.52296</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>SANTA MARIA LA CATOLICA</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-9.1401</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-78.50767999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>429</v>
-      </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-9.1401</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-78.50768</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>SEÑOR DE LA VIDA</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-9.12842</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-78.52357000000001</v>
-      </c>
-      <c r="I30" t="n">
-        <v>682</v>
-      </c>
-      <c r="J30" t="n">
-        <v>57</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-9.12842</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-78.52357</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>88400 JESUS DE NAZARETH</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-9.142505</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-78.502718</v>
-      </c>
-      <c r="I31" t="n">
-        <v>649</v>
-      </c>
-      <c r="J31" t="n">
-        <v>31</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-9.142505</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-78.502718</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>BUENA ESPERANZA</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-9.14348</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-78.50476999999999</v>
-      </c>
-      <c r="I32" t="n">
-        <v>415</v>
-      </c>
-      <c r="J32" t="n">
-        <v>26</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-9.14348</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-78.50477</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>415</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>JACQUES DELORS</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-9.11806</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-78.50726</v>
-      </c>
-      <c r="I33" t="n">
-        <v>373</v>
-      </c>
-      <c r="J33" t="n">
-        <v>20</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-9.11806</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-78.50726</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>MUNDO DE NIÑOS</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-9.12233</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-78.53373999999999</v>
-      </c>
-      <c r="I34" t="n">
-        <v>493</v>
-      </c>
-      <c r="J34" t="n">
-        <v>37</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-9.12233</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-78.53374</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>GARDNER SCHOOL</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-9.128970000000001</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-78.51837</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>1</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-9.12897</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-78.51837</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>88413</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-9.133190000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-78.49831</v>
-      </c>
-      <c r="I36" t="n">
-        <v>348</v>
-      </c>
-      <c r="J36" t="n">
-        <v>17</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-9.13319</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-78.49831</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>INNOVA SCHOOLS</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-9.127840000000001</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-78.53404</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1325</v>
-      </c>
-      <c r="J37" t="n">
-        <v>52</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-9.12784</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-78.53404</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1325</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>89541</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-9.136958999999999</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-78.492906</v>
-      </c>
-      <c r="I38" t="n">
-        <v>436</v>
-      </c>
-      <c r="J38" t="n">
-        <v>17</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-9.136959</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-78.492906</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>88417</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-9.136282</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-78.492909</v>
-      </c>
-      <c r="I39" t="n">
-        <v>376</v>
-      </c>
-      <c r="J39" t="n">
-        <v>15</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-9.136282</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-78.492909</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>88418</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-9.147883999999999</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-78.50089800000001</v>
-      </c>
-      <c r="I40" t="n">
-        <v>439</v>
-      </c>
-      <c r="J40" t="n">
-        <v>23</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-9.147884</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-78.500898</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>439</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>LA CASA DE LOS NIÑOS</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-9.125157</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-78.529363</v>
-      </c>
-      <c r="I41" t="n">
-        <v>46</v>
-      </c>
-      <c r="J41" t="n">
-        <v>6</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-9.125157</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-78.529363</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-9.129109</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-78.517708</v>
-      </c>
-      <c r="I42" t="n">
-        <v>289</v>
-      </c>
-      <c r="J42" t="n">
-        <v>19</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-9.129109</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-78.517708</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>89550 ANGEL ARNULFO RIOS DE LA CRUZ</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-9.14221</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-78.4881</v>
-      </c>
-      <c r="I43" t="n">
-        <v>338</v>
-      </c>
-      <c r="J43" t="n">
-        <v>14</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-9.14221</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-78.4881</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>89551</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-9.14265</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-78.48775999999999</v>
-      </c>
-      <c r="I44" t="n">
-        <v>224</v>
-      </c>
-      <c r="J44" t="n">
-        <v>14</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-9.14265</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-78.48776</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>2659</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-9.14662</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-78.49242</v>
-      </c>
-      <c r="I45" t="n">
-        <v>242</v>
-      </c>
-      <c r="J45" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-9.14662</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-78.49242</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-9.129619999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-78.52311</v>
-      </c>
-      <c r="I46" t="n">
-        <v>305</v>
-      </c>
-      <c r="J46" t="n">
-        <v>22</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-9.12962</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-78.52311</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>SONRISAS SCHOOL</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-9.129059</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-78.518064</v>
-      </c>
-      <c r="I47" t="n">
-        <v>67</v>
-      </c>
-      <c r="J47" t="n">
-        <v>8</v>
-      </c>
-      <c r="K47" t="n">
-        <v>1</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-9.129059</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-78.518064</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>622400</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VIRGEN DE LAS GRACIAS</t>
+          <t>GARDNER SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.11421</t>
+          <t>-9.12897</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.51354</t>
+          <t>-78.51837</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>844566</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.12403</t>
+          <t>-9.14662</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-78.52777</t>
+          <t>-78.49242</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>37720</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>88021 ALFONSO UGARTE</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.13482</t>
+          <t>-9.12403</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.51914</t>
+          <t>-78.52777</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>530900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88024</t>
+          <t>SANTA MARIA LA CATOLICA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.12237</t>
+          <t>-9.1401</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.54073</t>
+          <t>-78.50768</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>429</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>807583</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>88028 ALMIRANTE MIGUEL GRAU</t>
+          <t>89550 ANGEL ARNULFO RIOS DE LA CRUZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.11911</t>
+          <t>-9.14221</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.54417</t>
+          <t>-78.4881</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>338</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>833346</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>88047 AUGUSTO SALAZAR BONDY</t>
+          <t>89551</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.12723</t>
+          <t>-9.14265</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.52884</t>
+          <t>-78.48776</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>224</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>88061 JOSE ABELARDO QUIÑONES</t>
+          <t>NORTON SCHOOL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.11555</t>
+          <t>-9.1364</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.51435</t>
+          <t>-78.5208</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>229</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>777128</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88227 PEDRO PABLO ATUSPARIA</t>
+          <t>88417</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.12505</t>
+          <t>-9.136282</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-78.51515</t>
+          <t>-78.492909</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>625446</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88240 PAZ Y AMISTAD</t>
+          <t>88413</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.13137</t>
+          <t>-9.13319</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.51621</t>
+          <t>-78.49831</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>348</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>733894</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>88298 LUIS ALBERTO SANCHEZ</t>
+          <t>89541</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.10938</t>
+          <t>-9.136959</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.53254</t>
+          <t>-78.492906</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>436</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37961</t>
+          <t>802081</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88336 GASTON VIDAL PORTURAS</t>
+          <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.12065</t>
+          <t>-9.129109</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.5169</t>
+          <t>-78.517708</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>289</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37975</t>
+          <t>37876</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88388 SAN LUIS DE LA PAZ</t>
+          <t>88024</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.137669</t>
+          <t>-9.12237</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.510127</t>
+          <t>-78.54073</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>332</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>512538</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>REPUBLICA ARGENTINA</t>
+          <t>88404</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.12585</t>
+          <t>-9.14749</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.52682</t>
+          <t>-78.50353</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>463</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>603835</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>JACQUES DELORS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.12071</t>
+          <t>-9.11806</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-78.54867</t>
+          <t>-78.50726</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>373</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>847503</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>88389 JUAN VALER SANDOVAL</t>
+          <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.11655</t>
+          <t>-9.12962</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.50554</t>
+          <t>-78.52311</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>305</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>777133</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>R. F. S. DE YUGOSLAVIA</t>
+          <t>88418</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.13225</t>
+          <t>-9.147884</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.5205</t>
+          <t>-78.500898</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>439</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>578614</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.14711</t>
+          <t>-9.14348</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.50741</t>
+          <t>-78.50477</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>37881</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 14</t>
+          <t>88028 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.11353</t>
+          <t>-9.11911</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.536861</t>
+          <t>-78.54417</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>559</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CRISTO AMIGO</t>
+          <t>88240 PAZ Y AMISTAD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.12999</t>
+          <t>-9.13137</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.52722</t>
+          <t>-78.51621</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>625</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>531792</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>NORTON SCHOOL</t>
+          <t>88400 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.1364</t>
+          <t>-9.142505</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.5208</t>
+          <t>-78.502718</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>649</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>512581</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SEMILLITAS &amp; DOLORIER</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.12087</t>
+          <t>-9.11935</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.51751</t>
+          <t>-78.52296</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>725</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>622122</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE CERVELLO</t>
+          <t>MUNDO DE NIÑOS</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.12313</t>
+          <t>-9.12233</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.53166</t>
+          <t>-78.53374</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>493</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>512538</t>
+          <t>37942</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>88404</t>
+          <t>88298 LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.14749</t>
+          <t>-9.10938</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.50353</t>
+          <t>-78.53254</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>845</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>512581</t>
+          <t>38135</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>CRISTO AMIGO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-9.11935</t>
+          <t>-9.12999</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-78.52296</t>
+          <t>-78.52722</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>454</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>530900</t>
+          <t>38381</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA MARIA LA CATOLICA</t>
+          <t>SANTA MARIA DE CERVELLO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.1401</t>
+          <t>-9.12313</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.50768</t>
+          <t>-78.53166</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>784</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>531202</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA VIDA</t>
+          <t>R. F. S. DE YUGOSLAVIA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.12842</t>
+          <t>-9.13225</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.52357</t>
+          <t>-78.5205</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>756</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>531792</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>88400 JESUS DE NAZARETH</t>
+          <t>88061 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.142505</t>
+          <t>-9.11555</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.502718</t>
+          <t>-78.51435</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>578614</t>
+          <t>35226</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BUENA ESPERANZA</t>
+          <t>VIRGEN DE LAS GRACIAS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.14348</t>
+          <t>-9.11421</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.50477</t>
+          <t>-78.51354</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>737</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>603835</t>
+          <t>38084</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>JACQUES DELORS</t>
+          <t>88042</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.11806</t>
+          <t>-9.14711</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.50726</t>
+          <t>-78.50741</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>982</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>622122</t>
+          <t>690658</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>MUNDO DE NIÑOS</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.12233</t>
+          <t>-9.12784</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.53374</t>
+          <t>-78.53404</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>622400</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GARDNER SCHOOL</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.12897</t>
+          <t>-9.12071</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.51837</t>
+          <t>-78.54867</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>873</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>54</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>625446</t>
+          <t>531202</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>88413</t>
+          <t>SEÑOR DE LA VIDA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.13319</t>
+          <t>-9.12842</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.49831</t>
+          <t>-78.52357</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>682</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>690658</t>
+          <t>785576</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>LA CASA DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.12784</t>
+          <t>-9.125157</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.53404</t>
+          <t>-78.529363</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>733894</t>
+          <t>37975</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>89541</t>
+          <t>88388 SAN LUIS DE LA PAZ</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.136959</t>
+          <t>-9.137669</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.492906</t>
+          <t>-78.510127</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>777128</t>
+          <t>37923</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>88417</t>
+          <t>88227 PEDRO PABLO ATUSPARIA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-9.136282</t>
+          <t>-9.12505</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-78.492909</t>
+          <t>-78.51515</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>777133</t>
+          <t>38003</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>88418</t>
+          <t>88389 JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.147884</t>
+          <t>-9.11655</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.500898</t>
+          <t>-78.50554</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>65</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,37 +2919,37 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>785576</t>
+          <t>37862</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>LA CASA DE LOS NIÑOS</t>
+          <t>88021 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.125157</t>
+          <t>-9.13482</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.529363</t>
+          <t>-78.51914</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>802081</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>EL SEÑOR ES MI PASTOR</t>
+          <t>FE Y ALEGRIA 14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.129109</t>
+          <t>-9.11353</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.517708</t>
+          <t>-78.536861</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>807583</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>89550 ANGEL ARNULFO RIOS DE LA CRUZ</t>
+          <t>REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.14221</t>
+          <t>-9.12585</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.4881</t>
+          <t>-78.52682</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>79</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>833346</t>
+          <t>909529</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>89551</t>
+          <t>SONRISAS SCHOOL</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.14265</t>
+          <t>-9.129059</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.48776</t>
+          <t>-78.518064</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>67</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>844566</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>88336 GASTON VIDAL PORTURAS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.14662</t>
+          <t>-9.12065</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.49242</t>
+          <t>-78.5169</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>82</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>847503</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EL SEÑOR ES MI PASTOR</t>
+          <t>SEMILLITAS &amp; DOLORIER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.12962</t>
+          <t>-9.12087</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.52311</t>
+          <t>-78.51751</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>173</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>909529</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SONRISAS SCHOOL</t>
+          <t>88047 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.129059</t>
+          <t>-9.12723</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.518064</t>
+          <t>-78.52884</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>96</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>622400</t>
+          <t>909529</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GARDNER SCHOOL</t>
+          <t>SONRISAS SCHOOL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.12897</t>
+          <t>67</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-78.51837</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.129059</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-78.518064</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>37701</t>
+          <t>847503</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
+          <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.12503</t>
+          <t>305</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-78.5192</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-9.12962</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-78.52311</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -635,22 +635,22 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>-9.14662</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>-78.49242</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37720</t>
+          <t>833346</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1570</t>
+          <t>89551</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.12403</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-78.52777</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-9.14265</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-78.48776</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>530900</t>
+          <t>807583</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SANTA MARIA LA CATOLICA</t>
+          <t>89550 ANGEL ARNULFO RIOS DE LA CRUZ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.1401</t>
+          <t>338</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-78.50768</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>-9.14221</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.4881</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>807583</t>
+          <t>802081</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>89550 ANGEL ARNULFO RIOS DE LA CRUZ</t>
+          <t>EL SEÑOR ES MI PASTOR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.14221</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-78.4881</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>-9.129109</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.517708</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>833346</t>
+          <t>785576</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>89551</t>
+          <t>LA CASA DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.14265</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-78.48776</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>224</t>
+          <t>-9.125157</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-78.529363</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,32 +935,32 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>777133</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NORTON SCHOOL</t>
+          <t>88418</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.1364</t>
+          <t>439</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-78.5208</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>-9.147884</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-78.500898</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1007,22 +1007,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>-9.136282</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>-78.492909</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>625446</t>
+          <t>733894</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>88413</t>
+          <t>89541</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.13319</t>
+          <t>436</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-78.49831</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>-9.136959</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.492906</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>733894</t>
+          <t>690658</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>89541</t>
+          <t>INNOVA SCHOOLS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.136959</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-78.492906</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>-9.12784</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-78.53404</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>802081</t>
+          <t>625446</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EL SEÑOR ES MI PASTOR</t>
+          <t>88413</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.129109</t>
+          <t>348</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-78.517708</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>-9.13319</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-78.49831</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1245,37 +1245,37 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>622400</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88024</t>
+          <t>GARDNER SCHOOL</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.12237</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-78.54073</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>-9.12897</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.51837</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>512538</t>
+          <t>622122</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88404</t>
+          <t>MUNDO DE NIÑOS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.14749</t>
+          <t>493</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-78.50353</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>-9.12233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-78.53374</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1379,22 +1379,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>-9.11806</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>-78.50726</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>847503</t>
+          <t>578614</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EL SEÑOR ES MI PASTOR</t>
+          <t>BUENA ESPERANZA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.12962</t>
+          <t>415</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-78.52311</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>-9.14348</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-78.50477</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>777133</t>
+          <t>531792</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88418</t>
+          <t>88400 JESUS DE NAZARETH</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.147884</t>
+          <t>649</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-78.500898</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>-9.142505</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-78.502718</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>578614</t>
+          <t>531202</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BUENA ESPERANZA</t>
+          <t>SEÑOR DE LA VIDA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.14348</t>
+          <t>682</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-78.50477</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>-9.12842</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-78.52357</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>530900</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88028 ALMIRANTE MIGUEL GRAU</t>
+          <t>SANTA MARIA LA CATOLICA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.11911</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-78.54417</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>-9.1401</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>-78.50768</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>512581</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88240 PAZ Y AMISTAD</t>
+          <t>JESUS MAESTRO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.13137</t>
+          <t>725</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-78.51621</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>-9.11935</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-78.52296</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>512538</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MARIA DE LAS MERCEDES</t>
+          <t>88404</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-9.12559</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-78.52935</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>-9.14749</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.50353</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>531792</t>
+          <t>038512</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>88400 JESUS DE NAZARETH</t>
+          <t>EXPERIMENTAL UNIVERSIDAD NACIONAL DEL SANTA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-9.142505</t>
+          <t>698</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-78.502718</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>-9.12321</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>-78.51109</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>512581</t>
+          <t>038381</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>JESUS MAESTRO</t>
+          <t>SANTA MARIA DE CERVELLO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-9.11935</t>
+          <t>784</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-78.52296</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>-9.12313</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.53166</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1927,32 +1927,32 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>622122</t>
+          <t>038362</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>MUNDO DE NIÑOS</t>
+          <t>SEMILLITAS &amp; DOLORIER</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-9.12233</t>
+          <t>173</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-78.53374</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>-9.12087</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-78.51751</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>038296</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>EXPERIMENTAL UNIVERSIDAD NACIONAL DEL SANTA</t>
+          <t>NORTON SCHOOL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-9.12321</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-78.51109</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>-9.1364</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-78.5208</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>038258</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>88298 LUIS ALBERTO SANCHEZ</t>
+          <t>MARIA DE LAS MERCEDES</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-9.10938</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-78.53254</t>
+          <t>31</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>-9.12559</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-78.52935</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>038135</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2123,22 +2123,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
+          <t>454</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>-9.12999</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>-78.52722</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,32 +2175,32 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>038116</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SANTA MARIA DE CERVELLO</t>
+          <t>FE Y ALEGRIA 14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-9.12313</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-78.53166</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>-9.11353</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-78.536861</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>38017</t>
+          <t>038084</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>R. F. S. DE YUGOSLAVIA</t>
+          <t>88042</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-9.13225</t>
+          <t>982</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-78.5205</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>756</t>
+          <t>-9.14711</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>-78.50741</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>038017</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>88061 JOSE ABELARDO QUIÑONES</t>
+          <t>R. F. S. DE YUGOSLAVIA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-9.11555</t>
+          <t>756</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-78.51435</t>
+          <t>43</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-9.13225</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>-78.5205</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35226</t>
+          <t>038003</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>VIRGEN DE LAS GRACIAS</t>
+          <t>88389 JUAN VALER SANDOVAL</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-9.11421</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-78.51354</t>
+          <t>65</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>-9.11655</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>-78.50554</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,32 +2423,32 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>037999</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>VILLA MARIA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-9.14711</t>
+          <t>873</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-78.50741</t>
+          <t>54</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>-9.12071</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-78.54867</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>690658</t>
+          <t>037980</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>INNOVA SCHOOLS</t>
+          <t>REPUBLICA ARGENTINA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-9.12784</t>
+          <t>1615</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-78.53404</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>-9.12585</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-78.52682</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>037975</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>VILLA MARIA</t>
+          <t>88388 SAN LUIS DE LA PAZ</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-9.12071</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-78.54867</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>-9.137669</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>-78.510127</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>531202</t>
+          <t>037961</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SEÑOR DE LA VIDA</t>
+          <t>88336 GASTON VIDAL PORTURAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-9.12842</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-78.52357</t>
+          <t>82</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>-9.12065</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-78.5169</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,37 +2671,37 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>785576</t>
+          <t>037942</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LA CASA DE LOS NIÑOS</t>
+          <t>88298 LUIS ALBERTO SANCHEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-9.125157</t>
+          <t>845</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-78.529363</t>
+          <t>40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-9.10938</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>-78.53254</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37975</t>
+          <t>037937</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>88388 SAN LUIS DE LA PAZ</t>
+          <t>88240 PAZ Y AMISTAD</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-9.137669</t>
+          <t>625</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-78.510127</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t>-9.13137</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-78.51621</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37923</t>
+          <t>037923</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2805,22 +2805,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>1455</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>-9.12505</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>-78.51515</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1455</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>62</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>037904</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>88389 JUAN VALER SANDOVAL</t>
+          <t>88061 JOSE ABELARDO QUIÑONES</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-9.11655</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-78.50554</t>
+          <t>48</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>-9.11555</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>-78.51435</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>37862</t>
+          <t>037895</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>88021 ALFONSO UGARTE</t>
+          <t>88047 AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-9.13482</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-78.51914</t>
+          <t>96</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>-9.12723</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>-78.52884</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>037881</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 14</t>
+          <t>88028 ALMIRANTE MIGUEL GRAU</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-9.11353</t>
+          <t>559</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-78.536861</t>
+          <t>27</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>-9.11911</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-78.54417</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>37980</t>
+          <t>037876</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>REPUBLICA ARGENTINA</t>
+          <t>88024</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-9.12585</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-78.52682</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>-9.12237</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>-78.54073</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,37 +3105,37 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>909529</t>
+          <t>037862</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>SONRISAS SCHOOL</t>
+          <t>88021 ALFONSO UGARTE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-9.129059</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-78.518064</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-9.13482</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-78.51914</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>37961</t>
+          <t>037720</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>88336 GASTON VIDAL PORTURAS</t>
+          <t>1570</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-9.12065</t>
+          <t>224</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-78.5169</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>-9.12403</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-78.52777</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>037701</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>SEMILLITAS &amp; DOLORIER</t>
+          <t>1563 CRISTO REY AMIGO DE LOS NIÑOS</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-9.12087</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-78.51751</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>-9.12503</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-78.5192</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,32 +3291,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>37895</t>
+          <t>035226</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>88047 AUGUSTO SALAZAR BONDY</t>
+          <t>VIRGEN DE LAS GRACIAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-9.12723</t>
+          <t>737</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-78.52884</t>
+          <t>51</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>-9.11421</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-78.51354</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">

--- a/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
+++ b/ZonasEscolares/excels/ANCASH-SANTA-NUEVO_CHIMBOTE.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
